--- a/final_outputs/excel_tables/table_descriptive_stats.xlsx
+++ b/final_outputs/excel_tables/table_descriptive_stats.xlsx
@@ -472,22 +472,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2e-06</v>
+        <v>-3e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000394</v>
+        <v>0.002192</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.002766</v>
+        <v>-0.041089</v>
       </c>
       <c r="E2" t="n">
         <v>-1e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003251</v>
+        <v>0.032109</v>
       </c>
       <c r="G2" t="n">
-        <v>3526</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="3">
@@ -497,22 +497,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000394</v>
+        <v>0.000303</v>
       </c>
       <c r="C3" t="n">
-        <v>1.697329</v>
+        <v>1.689697</v>
       </c>
       <c r="D3" t="n">
         <v>-11.8979</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0955</v>
+        <v>-0.0929</v>
       </c>
       <c r="F3" t="n">
         <v>17.7581</v>
       </c>
       <c r="G3" t="n">
-        <v>3526</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="4">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.000226</v>
+        <v>0.000272</v>
       </c>
       <c r="C4" t="n">
-        <v>0.043947</v>
+        <v>0.043996</v>
       </c>
       <c r="D4" t="n">
         <v>-0.29</v>
@@ -537,7 +537,7 @@
         <v>0.298</v>
       </c>
       <c r="G4" t="n">
-        <v>3526</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="5">
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.7e-05</v>
+        <v>0.000179</v>
       </c>
       <c r="C5" t="n">
-        <v>0.040253</v>
+        <v>0.041009</v>
       </c>
       <c r="D5" t="n">
         <v>-0.352421</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.000489</v>
+        <v>-0.000457</v>
       </c>
       <c r="F5" t="n">
         <v>0.412784</v>
       </c>
       <c r="G5" t="n">
-        <v>3526</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="6">
@@ -572,22 +572,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.000182</v>
+        <v>-8.3e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.022937</v>
+        <v>0.023741</v>
       </c>
       <c r="D6" t="n">
         <v>-0.279761</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000757</v>
+        <v>0.000828</v>
       </c>
       <c r="F6" t="n">
         <v>0.190774</v>
       </c>
       <c r="G6" t="n">
-        <v>3526</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="7">
@@ -597,22 +597,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.000671</v>
+        <v>0.000637</v>
       </c>
       <c r="C7" t="n">
-        <v>0.030645</v>
+        <v>0.030478</v>
       </c>
       <c r="D7" t="n">
         <v>-0.432421</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000837</v>
+        <v>0.000753</v>
       </c>
       <c r="F7" t="n">
         <v>0.23923</v>
       </c>
       <c r="G7" t="n">
-        <v>3526</v>
+        <v>3611</v>
       </c>
     </row>
   </sheetData>

--- a/final_outputs/excel_tables/table_descriptive_stats.xlsx
+++ b/final_outputs/excel_tables/table_descriptive_stats.xlsx
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-3e-06</v>
+        <v>-4e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002192</v>
+        <v>0.000445</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.041089</v>
+        <v>-0.003935</v>
       </c>
       <c r="E2" t="n">
         <v>-1e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>0.032109</v>
+        <v>0.004236</v>
       </c>
       <c r="G2" t="n">
         <v>3611</v>
